--- a/src/assets/employees/manel.xlsx
+++ b/src/assets/employees/manel.xlsx
@@ -432,8 +432,8 @@
       <c r="D2" t="str">
         <v/>
       </c>
-      <c r="E2" t="str">
-        <v/>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2" t="str">
         <v/>
